--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlRepoPledgeSearch001.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlRepoPledgeSearch001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BS\tams\tams-invest-parent\tams-invest-portfolio\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="600" yWindow="135" windowWidth="19395" windowHeight="7605"/>
+    <workbookView xWindow="1530" yWindow="135" windowWidth="19395" windowHeight="7605"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>组合代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +88,10 @@
   </si>
   <si>
     <t>业务类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易对手</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -161,7 +170,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -203,7 +212,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -238,7 +247,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
@@ -460,7 +469,7 @@
     <col min="15" max="15" width="19.25" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -511,6 +520,9 @@
       </c>
       <c r="Q1" t="s">
         <v>14</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
